--- a/DTY Jun26產銷260527-1100+500+100_clear.xlsx
+++ b/DTY Jun26產銷260527-1100+500+100_clear.xlsx
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>150/48/2 CE</t>
+          <t>150/48 CE</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>FP80xxxR(L57)</t>
+          <t>FP80148R</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>85/36 SDR</t>
+          <t>80/36 SDR</t>
         </is>
       </c>
       <c r="K18" s="4" t="n">
@@ -1628,7 +1628,7 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>FP80xxxR(L57)</t>
+          <t>FP80148R</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>FP80xxxR(L57)</t>
+          <t>FP80148R</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
